--- a/Ingresos_Tumaco.xlsx
+++ b/Ingresos_Tumaco.xlsx
@@ -1,26 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\almun\OneDrive - Universidad Nacional de Colombia\Escritorio\A Ingresos - tablas segmentadas descargar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mjimenalopez/GitHub/DatosMemoria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB2C144B-BE81-4F7A-B3BF-DF2ACFC10E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F791DB3-4731-D34A-BAF4-057D7F004B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{51C11BDB-4639-40B1-8165-255053E8BF8C}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="37200" windowHeight="18760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -494,25 +491,10 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -577,6 +559,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="3"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -911,2551 +908,2706 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8B5D6AA-7BDC-4976-A4C0-8D733D5F4A2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="11.42578125" hidden="1"/>
+    <col min="13" max="13" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="29" width="0" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="11.5" hidden="1" customWidth="1"/>
+    <col min="31" max="16384" width="11.5" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="49"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="45">
         <v>2016</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="3">
+      <c r="C3" s="46"/>
+      <c r="D3" s="45">
         <v>2017</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="3">
+      <c r="E3" s="46"/>
+      <c r="F3" s="45">
         <v>2018</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="3">
+      <c r="G3" s="46"/>
+      <c r="H3" s="45">
         <v>2019</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="3">
+      <c r="I3" s="46"/>
+      <c r="J3" s="45">
         <v>2020</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="3">
+      <c r="K3" s="46"/>
+      <c r="L3" s="45">
         <v>2021</v>
       </c>
-      <c r="M3" s="4"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="6" t="s">
+      <c r="M3" s="46"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="51"/>
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="4">
         <f t="shared" ref="B5:M5" si="0">+B6+B40</f>
         <v>15133974347</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="5">
         <f t="shared" si="0"/>
         <v>11796857808</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="5">
         <f t="shared" si="0"/>
-        <v>20386682264</v>
-      </c>
-      <c r="E5" s="10">
+        <v>20714786928</v>
+      </c>
+      <c r="E5" s="5">
         <f t="shared" si="0"/>
-        <v>18936064975</v>
-      </c>
-      <c r="F5" s="9">
+        <v>18981737902</v>
+      </c>
+      <c r="F5" s="4">
         <f t="shared" si="0"/>
         <v>27970768480</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="5">
         <f t="shared" si="0"/>
         <v>28194602440</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="4">
         <f t="shared" si="0"/>
         <v>13210378121</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="5">
         <f t="shared" si="0"/>
         <v>13782539840</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="4">
         <f t="shared" si="0"/>
         <v>28746025017</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="5">
         <f t="shared" si="0"/>
         <v>29182798908</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="4">
         <f t="shared" si="0"/>
         <v>19776495230</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="5">
         <f t="shared" si="0"/>
         <v>19301158068</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="48" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+    <row r="6" spans="1:13" s="43" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="7">
         <f t="shared" ref="B6:M6" si="1">+B7+B32+B35</f>
         <v>10899750737</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="8">
         <f t="shared" si="1"/>
         <v>9184845950</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="7">
         <f t="shared" si="1"/>
         <v>17642712844</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="8">
         <f t="shared" si="1"/>
         <v>17005260089</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="7">
         <f t="shared" si="1"/>
         <v>22777771818</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="8">
         <f t="shared" si="1"/>
         <v>23136237070</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="7">
         <f t="shared" si="1"/>
         <v>11049760895</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="8">
         <f t="shared" si="1"/>
         <v>11778385127</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="7">
         <f t="shared" si="1"/>
         <v>27794146567</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="8">
         <f t="shared" si="1"/>
         <v>28392728912</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="7">
         <f t="shared" si="1"/>
         <v>18749989799</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="8">
         <f t="shared" si="1"/>
         <v>18649736310</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="10">
         <f t="shared" ref="B7:M7" si="2">+B8+B25</f>
         <v>1308266154</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="11">
         <f t="shared" si="2"/>
         <v>1393361367</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="10">
         <f t="shared" si="2"/>
         <v>8671564527</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="11">
         <f t="shared" si="2"/>
         <v>8034111772</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="10">
         <f t="shared" si="2"/>
         <v>9497244487</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="11">
         <f t="shared" si="2"/>
         <v>9855709739</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="10">
         <f t="shared" si="2"/>
         <v>6409514099</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="11">
         <f t="shared" si="2"/>
         <v>7138138331</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="10">
         <f t="shared" si="2"/>
         <v>24391832078</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="11">
         <f t="shared" si="2"/>
         <v>24995632509</v>
       </c>
-      <c r="L7" s="15">
+      <c r="L7" s="10">
         <f t="shared" si="2"/>
         <v>15413542605</v>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="11">
         <f t="shared" si="2"/>
         <v>15313289116</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+    <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="18">
-        <f>+B9+B15+B17+B21</f>
+      <c r="B8" s="13">
+        <f t="shared" ref="B8:M8" si="3">+B9+B15+B17+B21</f>
         <v>1083566384</v>
       </c>
-      <c r="C8" s="19">
-        <f>+C9+C15+C17+C21</f>
+      <c r="C8" s="14">
+        <f t="shared" si="3"/>
         <v>1120644099</v>
       </c>
-      <c r="D8" s="18">
-        <f t="shared" ref="D8:M8" si="3">+D9+D15+D17+D21</f>
+      <c r="D8" s="13">
+        <f t="shared" si="3"/>
         <v>1517238966</v>
       </c>
-      <c r="E8" s="19">
-        <f>+E9+E15+E17+E21</f>
+      <c r="E8" s="14">
+        <f t="shared" si="3"/>
         <v>1556894222</v>
       </c>
-      <c r="F8" s="18">
-        <f>+F9+F15+F17+F21</f>
+      <c r="F8" s="13">
+        <f t="shared" si="3"/>
         <v>2000401804</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="14">
         <f t="shared" si="3"/>
         <v>1918082524</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="13">
         <f t="shared" si="3"/>
         <v>2161557470</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="14">
         <f t="shared" si="3"/>
         <v>2258209245</v>
       </c>
-      <c r="J8" s="18">
+      <c r="J8" s="13">
         <f t="shared" si="3"/>
         <v>2463838360</v>
       </c>
-      <c r="K8" s="19">
+      <c r="K8" s="14">
         <f t="shared" si="3"/>
         <v>2195937294</v>
       </c>
-      <c r="L8" s="18">
+      <c r="L8" s="13">
         <f t="shared" si="3"/>
         <v>2229547843</v>
       </c>
-      <c r="M8" s="19">
+      <c r="M8" s="14">
         <f t="shared" si="3"/>
         <v>1673533977</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
+    <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="16">
+        <f t="shared" ref="B9:M9" si="4">SUM(B10:B14)</f>
         <v>747459897</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="17">
+        <f t="shared" si="4"/>
         <v>767732942</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="16">
+        <f t="shared" si="4"/>
         <v>962300525</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="17">
+        <f t="shared" si="4"/>
         <v>941744041</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="16">
+        <f t="shared" si="4"/>
         <v>1472269484</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="17">
+        <f t="shared" si="4"/>
         <v>1249714769</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="16">
+        <f t="shared" si="4"/>
         <v>1776834782</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="17">
+        <f t="shared" si="4"/>
         <v>1795662529</v>
       </c>
-      <c r="J9" s="21">
+      <c r="J9" s="16">
+        <f t="shared" si="4"/>
         <v>2313838360</v>
       </c>
-      <c r="K9" s="22">
+      <c r="K9" s="17">
+        <f t="shared" si="4"/>
         <v>2129297101</v>
       </c>
-      <c r="L9" s="21">
+      <c r="L9" s="16">
+        <f t="shared" si="4"/>
         <v>2057192083</v>
       </c>
-      <c r="M9" s="22">
+      <c r="M9" s="17">
+        <f t="shared" si="4"/>
         <v>1506137585</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
+    <row r="10" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="19">
         <v>28719860</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="20">
         <v>28719860</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="19">
         <v>30386000</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="20">
         <v>30386000</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="19">
         <v>31662212</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="20">
         <v>31702212</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="19">
         <v>32707065</v>
       </c>
-      <c r="I10" s="25">
+      <c r="I10" s="20">
         <v>32707065</v>
       </c>
-      <c r="J10" s="24">
+      <c r="J10" s="19">
         <v>32707065</v>
       </c>
-      <c r="K10" s="25">
+      <c r="K10" s="20">
         <v>24103416</v>
       </c>
-      <c r="L10" s="24">
+      <c r="L10" s="19">
         <v>32707065</v>
       </c>
-      <c r="M10" s="25">
+      <c r="M10" s="20">
         <v>18359736</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="23" t="s">
+    <row r="11" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="19">
         <v>717390037</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="20">
         <v>726604282</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="19">
         <v>48150000</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="20">
         <v>29892955</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="19">
         <v>58932000</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="20">
         <v>15402736</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="19">
         <v>40866300</v>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="20">
         <v>46456918</v>
       </c>
-      <c r="J11" s="24">
+      <c r="J11" s="19">
         <v>46607580</v>
       </c>
-      <c r="K11" s="25">
+      <c r="K11" s="20">
         <v>7443724</v>
       </c>
-      <c r="L11" s="24">
+      <c r="L11" s="19">
         <v>66454622</v>
       </c>
-      <c r="M11" s="25">
+      <c r="M11" s="20">
         <v>28223550</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="23" t="s">
+    <row r="12" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="19">
         <v>1350000</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="20">
         <v>3447107</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="19">
         <v>4815000</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="20">
         <v>5061849</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="19">
         <v>5893200</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="20">
         <v>2517499</v>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="19">
         <v>4807800</v>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="20">
         <v>4310385</v>
       </c>
-      <c r="J12" s="24">
+      <c r="J12" s="19">
         <v>5178100</v>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="20">
         <v>969484</v>
       </c>
-      <c r="L12" s="24">
+      <c r="L12" s="19">
         <v>6765876</v>
       </c>
-      <c r="M12" s="25">
+      <c r="M12" s="20">
         <v>2244774</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
+    <row r="13" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="24">
+      <c r="B13" s="19"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="19">
         <v>1696049717</v>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="20">
         <v>1696049717</v>
       </c>
-      <c r="J13" s="24">
+      <c r="J13" s="19">
         <v>2194079215</v>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="20">
         <v>2094079215</v>
       </c>
-      <c r="L13" s="24">
+      <c r="L13" s="19">
         <v>1901355479</v>
       </c>
-      <c r="M13" s="25">
+      <c r="M13" s="20">
         <v>1451355479</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="23" t="s">
+    <row r="14" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="24">
-        <v>0</v>
-      </c>
-      <c r="C14" s="25">
+      <c r="B14" s="19">
+        <v>0</v>
+      </c>
+      <c r="C14" s="20">
         <v>8961693</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="19">
         <v>878949525</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="20">
         <v>876403237</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="19">
         <v>1375782072</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="20">
         <v>1200092322</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="19">
         <v>2403900</v>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="20">
         <v>16138444</v>
       </c>
-      <c r="J14" s="24">
+      <c r="J14" s="19">
         <v>35266400</v>
       </c>
-      <c r="K14" s="25">
+      <c r="K14" s="20">
         <v>2701262</v>
       </c>
-      <c r="L14" s="24">
+      <c r="L14" s="19">
         <v>49909041</v>
       </c>
-      <c r="M14" s="25">
+      <c r="M14" s="20">
         <v>5954046</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="16">
+        <f t="shared" ref="B15:G15" si="5">SUM(B16:B16)</f>
         <v>150000000</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="17">
+        <f t="shared" si="5"/>
         <v>149400000</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="16">
+        <f t="shared" si="5"/>
         <v>300000000</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="17">
+        <f t="shared" si="5"/>
         <v>300000000</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="16">
+        <f t="shared" si="5"/>
         <v>100000000</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="17">
+        <f t="shared" si="5"/>
         <v>300000000</v>
       </c>
-      <c r="H15" s="21">
-        <v>0</v>
-      </c>
-      <c r="I15" s="22">
-        <v>0</v>
-      </c>
-      <c r="J15" s="21">
-        <v>0</v>
-      </c>
-      <c r="K15" s="22">
-        <v>0</v>
-      </c>
-      <c r="L15" s="21">
-        <v>0</v>
-      </c>
-      <c r="M15" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="H15" s="16">
+        <v>0</v>
+      </c>
+      <c r="I15" s="17">
+        <v>0</v>
+      </c>
+      <c r="J15" s="16">
+        <v>0</v>
+      </c>
+      <c r="K15" s="17">
+        <v>0</v>
+      </c>
+      <c r="L15" s="16">
+        <v>0</v>
+      </c>
+      <c r="M15" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="19">
         <v>150000000</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="20">
         <v>149400000</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="19">
         <v>300000000</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="20">
         <v>300000000</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="19">
         <v>100000000</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="20">
         <v>300000000</v>
       </c>
-      <c r="H16" s="24"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="25"/>
-    </row>
-    <row r="17" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
+      <c r="H16" s="19"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="20"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="16">
+        <f t="shared" ref="B17:M17" si="6">SUM(B18:B20)</f>
         <v>186106487</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="17">
+        <f t="shared" si="6"/>
         <v>203511157</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="16">
+        <f t="shared" si="6"/>
         <v>200469725</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="17">
+        <f t="shared" si="6"/>
         <v>312423387</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="16">
+        <f t="shared" si="6"/>
         <v>180000000</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="17">
+        <f t="shared" si="6"/>
         <v>120235435</v>
       </c>
-      <c r="H17" s="21">
+      <c r="H17" s="16">
+        <f t="shared" si="6"/>
         <v>374821808</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="17">
+        <f t="shared" si="6"/>
         <v>452645836</v>
       </c>
-      <c r="J17" s="21">
+      <c r="J17" s="16">
+        <f t="shared" si="6"/>
         <v>150000000</v>
       </c>
-      <c r="K17" s="22">
+      <c r="K17" s="17">
+        <f t="shared" si="6"/>
         <v>66640193</v>
       </c>
-      <c r="L17" s="21">
+      <c r="L17" s="16">
+        <f t="shared" si="6"/>
         <v>75000000</v>
       </c>
-      <c r="M17" s="22">
+      <c r="M17" s="17">
+        <f t="shared" si="6"/>
         <v>118297073</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="23" t="s">
+    <row r="18" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="19">
         <v>66219160</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="20">
         <v>83623830</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="19">
         <v>168313684</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="20">
         <v>294422899</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="19">
         <v>180000000</v>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="20">
         <v>120235435</v>
       </c>
-      <c r="H18" s="24">
+      <c r="H18" s="19">
         <v>374821808</v>
       </c>
-      <c r="I18" s="25">
+      <c r="I18" s="20">
         <v>452642028</v>
       </c>
-      <c r="J18" s="24">
+      <c r="J18" s="19">
         <v>150000000</v>
       </c>
-      <c r="K18" s="25">
+      <c r="K18" s="20">
         <v>66066455</v>
       </c>
-      <c r="L18" s="24">
+      <c r="L18" s="19">
         <v>75000000</v>
       </c>
-      <c r="M18" s="25">
+      <c r="M18" s="20">
         <v>118276073</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="23" t="s">
+    <row r="19" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="19">
         <v>119887327</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="20">
         <v>119887327</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="19">
         <v>32156041</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="20">
         <v>14436041</v>
       </c>
-      <c r="F19" s="24"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="25"/>
-    </row>
-    <row r="20" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="23" t="s">
+      <c r="F19" s="19"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="20"/>
+    </row>
+    <row r="20" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="24"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="24">
-        <v>0</v>
-      </c>
-      <c r="E20" s="25">
+      <c r="B20" s="19"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="19">
+        <v>0</v>
+      </c>
+      <c r="E20" s="20">
         <v>3564447</v>
       </c>
-      <c r="F20" s="24"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="24">
-        <v>0</v>
-      </c>
-      <c r="I20" s="25">
+      <c r="F20" s="19"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="19">
+        <v>0</v>
+      </c>
+      <c r="I20" s="20">
         <v>3808</v>
       </c>
-      <c r="J20" s="24">
-        <v>0</v>
-      </c>
-      <c r="K20" s="25">
+      <c r="J20" s="19">
+        <v>0</v>
+      </c>
+      <c r="K20" s="20">
         <v>573738</v>
       </c>
-      <c r="L20" s="24">
-        <v>0</v>
-      </c>
-      <c r="M20" s="25">
+      <c r="L20" s="19">
+        <v>0</v>
+      </c>
+      <c r="M20" s="20">
         <v>21000</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="21">
-        <v>0</v>
-      </c>
-      <c r="C21" s="22">
-        <v>0</v>
-      </c>
-      <c r="D21" s="21">
+      <c r="B21" s="16">
+        <v>0</v>
+      </c>
+      <c r="C21" s="17">
+        <v>0</v>
+      </c>
+      <c r="D21" s="16">
+        <f t="shared" ref="D21:I21" si="7">SUM(D22:D24)</f>
         <v>54468716</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="17">
+        <f t="shared" si="7"/>
         <v>2726794</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="16">
+        <f t="shared" si="7"/>
         <v>248132320</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="17">
+        <f t="shared" si="7"/>
         <v>248132320</v>
       </c>
-      <c r="H21" s="21">
+      <c r="H21" s="16">
+        <f t="shared" si="7"/>
         <v>9900880</v>
       </c>
-      <c r="I21" s="22">
+      <c r="I21" s="17">
+        <f t="shared" si="7"/>
         <v>9900880</v>
       </c>
-      <c r="J21" s="21">
-        <v>0</v>
-      </c>
-      <c r="K21" s="22">
-        <v>0</v>
-      </c>
-      <c r="L21" s="21">
+      <c r="J21" s="16">
+        <v>0</v>
+      </c>
+      <c r="K21" s="17">
+        <v>0</v>
+      </c>
+      <c r="L21" s="16">
+        <f>SUM(L22:L24)</f>
         <v>97355760</v>
       </c>
-      <c r="M21" s="22">
+      <c r="M21" s="17">
+        <f>SUM(M22:M24)</f>
         <v>49099319</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="23" t="s">
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="21">
+      <c r="B22" s="16"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="16">
         <v>26351639</v>
       </c>
-      <c r="E22" s="22">
-        <v>0</v>
-      </c>
-      <c r="F22" s="21">
+      <c r="E22" s="17">
+        <v>0</v>
+      </c>
+      <c r="F22" s="16">
         <v>199087420</v>
       </c>
-      <c r="G22" s="22">
+      <c r="G22" s="17">
         <v>198311051</v>
       </c>
-      <c r="H22" s="21"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="21">
+      <c r="H22" s="16"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="16">
         <v>13636340</v>
       </c>
-      <c r="M22" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="23" t="s">
+      <c r="M22" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="21">
+      <c r="B23" s="16"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="16">
         <v>28117077</v>
       </c>
-      <c r="E23" s="22">
+      <c r="E23" s="17">
         <v>2726794</v>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="16">
         <v>24044900</v>
       </c>
-      <c r="G23" s="22">
+      <c r="G23" s="17">
         <v>24821269</v>
       </c>
-      <c r="H23" s="21"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="22"/>
-    </row>
-    <row r="24" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="23" t="s">
+      <c r="H23" s="16"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="17"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="26">
+      <c r="B24" s="21"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="21">
         <v>25000000</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="22">
         <v>25000000</v>
       </c>
-      <c r="H24" s="26">
+      <c r="H24" s="21">
         <v>9900880</v>
       </c>
-      <c r="I24" s="27">
+      <c r="I24" s="22">
         <v>9900880</v>
       </c>
-      <c r="J24" s="26"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="26">
+      <c r="J24" s="21"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="21">
         <v>83719420</v>
       </c>
-      <c r="M24" s="27">
+      <c r="M24" s="22">
         <v>49099319</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="18">
-        <f t="shared" ref="B25:M25" si="4">+B26+B28+B31</f>
+      <c r="B25" s="13">
+        <f t="shared" ref="B25:M25" si="8">+B26+B28+B31</f>
         <v>224699770</v>
       </c>
-      <c r="C25" s="19">
-        <f t="shared" si="4"/>
+      <c r="C25" s="14">
+        <f t="shared" si="8"/>
         <v>272717268</v>
       </c>
-      <c r="D25" s="18">
-        <f t="shared" si="4"/>
+      <c r="D25" s="13">
+        <f t="shared" si="8"/>
         <v>7154325561</v>
       </c>
-      <c r="E25" s="19">
-        <f t="shared" si="4"/>
+      <c r="E25" s="14">
+        <f t="shared" si="8"/>
         <v>6477217550</v>
       </c>
-      <c r="F25" s="18">
-        <f t="shared" si="4"/>
+      <c r="F25" s="13">
+        <f t="shared" si="8"/>
         <v>7496842683</v>
       </c>
-      <c r="G25" s="19">
-        <f t="shared" si="4"/>
+      <c r="G25" s="14">
+        <f t="shared" si="8"/>
         <v>7937627215</v>
       </c>
-      <c r="H25" s="18">
-        <f t="shared" si="4"/>
+      <c r="H25" s="13">
+        <f t="shared" si="8"/>
         <v>4247956629</v>
       </c>
-      <c r="I25" s="19">
-        <f t="shared" si="4"/>
+      <c r="I25" s="14">
+        <f t="shared" si="8"/>
         <v>4879929086</v>
       </c>
-      <c r="J25" s="18">
-        <f t="shared" si="4"/>
+      <c r="J25" s="13">
+        <f t="shared" si="8"/>
         <v>21927993718</v>
       </c>
-      <c r="K25" s="19">
-        <f t="shared" si="4"/>
+      <c r="K25" s="14">
+        <f t="shared" si="8"/>
         <v>22799695215</v>
       </c>
-      <c r="L25" s="18">
-        <f t="shared" si="4"/>
+      <c r="L25" s="13">
+        <f t="shared" si="8"/>
         <v>13183994762</v>
       </c>
-      <c r="M25" s="19">
-        <f t="shared" si="4"/>
+      <c r="M25" s="14">
+        <f t="shared" si="8"/>
         <v>13639755139</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="16">
+        <f t="shared" ref="B26:M26" si="9">SUM(B27:B27)</f>
         <v>72436948</v>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="17">
+        <f t="shared" si="9"/>
         <v>124383018</v>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="16">
+        <f t="shared" si="9"/>
         <v>47202897</v>
       </c>
-      <c r="E26" s="22">
+      <c r="E26" s="17">
+        <f t="shared" si="9"/>
         <v>245511417</v>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="16">
+        <f t="shared" si="9"/>
         <v>30000000</v>
       </c>
-      <c r="G26" s="22">
+      <c r="G26" s="17">
+        <f t="shared" si="9"/>
         <v>470784532</v>
       </c>
-      <c r="H26" s="21">
-        <v>20000000</v>
-      </c>
-      <c r="I26" s="22">
-        <v>651972457</v>
-      </c>
-      <c r="J26" s="21">
-        <v>6500000</v>
-      </c>
-      <c r="K26" s="22">
-        <v>891166756</v>
-      </c>
-      <c r="L26" s="21">
-        <v>20000000</v>
-      </c>
-      <c r="M26" s="22">
-        <v>475760377</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" s="49" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="24">
-        <v>72436948</v>
-      </c>
-      <c r="C27" s="25">
-        <v>124383018</v>
-      </c>
-      <c r="D27" s="24">
-        <v>47202897</v>
-      </c>
-      <c r="E27" s="25">
-        <v>245511417</v>
-      </c>
-      <c r="F27" s="24">
-        <v>30000000</v>
-      </c>
-      <c r="G27" s="25">
-        <v>470784532</v>
-      </c>
-      <c r="H27" s="24">
-        <v>20000000</v>
-      </c>
-      <c r="I27" s="25">
-        <v>651972457</v>
-      </c>
-      <c r="J27" s="24">
-        <v>6500000</v>
-      </c>
-      <c r="K27" s="25">
-        <v>891166756</v>
-      </c>
-      <c r="L27" s="24">
-        <v>20000000</v>
-      </c>
-      <c r="M27" s="25">
-        <v>475760377</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="21">
-        <v>130039513</v>
-      </c>
-      <c r="C28" s="22">
-        <v>126110941</v>
-      </c>
-      <c r="D28" s="21">
-        <v>6231706133</v>
-      </c>
-      <c r="E28" s="22">
-        <v>6231706133</v>
-      </c>
-      <c r="F28" s="21">
-        <v>674756823</v>
-      </c>
-      <c r="G28" s="22">
-        <v>674756823</v>
-      </c>
-      <c r="H28" s="21">
-        <v>3597286944</v>
-      </c>
-      <c r="I28" s="22">
-        <v>3597286944</v>
-      </c>
-      <c r="J28" s="21">
-        <v>21290824033</v>
-      </c>
-      <c r="K28" s="22">
-        <v>21277858774</v>
-      </c>
-      <c r="L28" s="21">
-        <v>13163994762</v>
-      </c>
-      <c r="M28" s="22">
-        <v>13163994762</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" s="49" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="24">
-        <v>126110941</v>
-      </c>
-      <c r="C29" s="25">
-        <v>126110941</v>
-      </c>
-      <c r="D29" s="24">
-        <v>5845009568</v>
-      </c>
-      <c r="E29" s="25">
-        <v>5845009568</v>
-      </c>
-      <c r="F29" s="24">
-        <v>666556823</v>
-      </c>
-      <c r="G29" s="25">
-        <v>666556823</v>
-      </c>
-      <c r="H29" s="24">
-        <v>510155245</v>
-      </c>
-      <c r="I29" s="25">
-        <v>510155245</v>
-      </c>
-      <c r="J29" s="24">
-        <v>21290824033</v>
-      </c>
-      <c r="K29" s="25">
-        <v>21277858774</v>
-      </c>
-      <c r="L29" s="24">
-        <v>12797994762</v>
-      </c>
-      <c r="M29" s="25">
-        <v>12797994762</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="B30" s="24">
-        <v>3928572</v>
-      </c>
-      <c r="C30" s="25">
-        <v>0</v>
-      </c>
-      <c r="D30" s="24">
-        <v>386696565</v>
-      </c>
-      <c r="E30" s="25">
-        <v>386696565</v>
-      </c>
-      <c r="F30" s="24">
-        <v>8200000</v>
-      </c>
-      <c r="G30" s="25">
-        <v>8200000</v>
-      </c>
-      <c r="H30" s="24">
-        <v>3087131699</v>
-      </c>
-      <c r="I30" s="25">
-        <v>3087131699</v>
-      </c>
-      <c r="J30" s="24">
-        <v>0</v>
-      </c>
-      <c r="K30" s="25">
-        <v>0</v>
-      </c>
-      <c r="L30" s="24">
-        <v>366000000</v>
-      </c>
-      <c r="M30" s="25">
-        <v>366000000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="26">
-        <v>22223309</v>
-      </c>
-      <c r="C31" s="27">
-        <v>22223309</v>
-      </c>
-      <c r="D31" s="26">
-        <v>875416531</v>
-      </c>
-      <c r="E31" s="27">
-        <v>0</v>
-      </c>
-      <c r="F31" s="26">
-        <v>6792085860</v>
-      </c>
-      <c r="G31" s="27">
-        <v>6792085860</v>
-      </c>
-      <c r="H31" s="26">
-        <v>630669685</v>
-      </c>
-      <c r="I31" s="27">
-        <v>630669685</v>
-      </c>
-      <c r="J31" s="26">
-        <v>630669685</v>
-      </c>
-      <c r="K31" s="27">
-        <v>630669685</v>
-      </c>
-      <c r="L31" s="26"/>
-      <c r="M31" s="27"/>
-    </row>
-    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="B32" s="30">
-        <f t="shared" ref="B32:M32" si="5">SUM(B33:B33)</f>
-        <v>5800000000</v>
-      </c>
-      <c r="C32" s="31">
-        <f t="shared" si="5"/>
-        <v>4000000000</v>
-      </c>
-      <c r="D32" s="30">
-        <f t="shared" si="5"/>
-        <v>5000000000</v>
-      </c>
-      <c r="E32" s="31">
-        <f t="shared" si="5"/>
-        <v>5000000000</v>
-      </c>
-      <c r="F32" s="30">
-        <f t="shared" si="5"/>
-        <v>12328777860</v>
-      </c>
-      <c r="G32" s="31">
-        <f t="shared" si="5"/>
-        <v>12328777860</v>
-      </c>
-      <c r="H32" s="30">
-        <f t="shared" si="5"/>
-        <v>3004655819</v>
-      </c>
-      <c r="I32" s="31">
-        <f t="shared" si="5"/>
-        <v>3004655819</v>
-      </c>
-      <c r="J32" s="30">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K32" s="31">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L32" s="30">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M32" s="31">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B33" s="33">
-        <v>5800000000</v>
-      </c>
-      <c r="C33" s="34">
-        <v>4000000000</v>
-      </c>
-      <c r="D33" s="33">
-        <v>5000000000</v>
-      </c>
-      <c r="E33" s="34">
-        <v>5000000000</v>
-      </c>
-      <c r="F33" s="33">
-        <v>12328777860</v>
-      </c>
-      <c r="G33" s="34">
-        <v>12328777860</v>
-      </c>
-      <c r="H33" s="33">
-        <v>3004655819</v>
-      </c>
-      <c r="I33" s="34">
-        <v>3004655819</v>
-      </c>
-      <c r="J33" s="33">
-        <v>0</v>
-      </c>
-      <c r="K33" s="34">
-        <v>0</v>
-      </c>
-      <c r="L33" s="33">
-        <v>0</v>
-      </c>
-      <c r="M33" s="34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="24">
-        <v>5800000000</v>
-      </c>
-      <c r="C34" s="25">
-        <v>4000000000</v>
-      </c>
-      <c r="D34" s="24">
-        <v>5000000000</v>
-      </c>
-      <c r="E34" s="25">
-        <v>5000000000</v>
-      </c>
-      <c r="F34" s="24">
-        <v>12328777860</v>
-      </c>
-      <c r="G34" s="25">
-        <v>12328777860</v>
-      </c>
-      <c r="H34" s="24">
-        <v>3004655819</v>
-      </c>
-      <c r="I34" s="25">
-        <v>3004655819</v>
-      </c>
-      <c r="J34" s="24">
-        <v>0</v>
-      </c>
-      <c r="K34" s="25">
-        <v>0</v>
-      </c>
-      <c r="L34" s="24">
-        <v>0</v>
-      </c>
-      <c r="M34" s="25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" s="30">
-        <f>+B36+B38</f>
-        <v>3791484583</v>
-      </c>
-      <c r="C35" s="31">
-        <f t="shared" ref="C35:M35" si="6">+C36+C38</f>
-        <v>3791484583</v>
-      </c>
-      <c r="D35" s="30">
-        <f t="shared" si="6"/>
-        <v>3971148317</v>
-      </c>
-      <c r="E35" s="31">
-        <f t="shared" si="6"/>
-        <v>3971148317</v>
-      </c>
-      <c r="F35" s="30">
-        <f t="shared" si="6"/>
-        <v>951749471</v>
-      </c>
-      <c r="G35" s="31">
-        <f t="shared" si="6"/>
-        <v>951749471</v>
-      </c>
-      <c r="H35" s="30">
-        <f t="shared" si="6"/>
-        <v>1635590977</v>
-      </c>
-      <c r="I35" s="31">
-        <f t="shared" si="6"/>
-        <v>1635590977</v>
-      </c>
-      <c r="J35" s="30">
-        <f t="shared" si="6"/>
-        <v>3402314489</v>
-      </c>
-      <c r="K35" s="31">
-        <f t="shared" si="6"/>
-        <v>3397096403</v>
-      </c>
-      <c r="L35" s="30">
-        <f t="shared" si="6"/>
-        <v>3336447194</v>
-      </c>
-      <c r="M35" s="31">
-        <f t="shared" si="6"/>
-        <v>3336447194</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="33">
-        <v>0</v>
-      </c>
-      <c r="C36" s="34">
-        <v>0</v>
-      </c>
-      <c r="D36" s="33"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="33">
-        <v>212874888</v>
-      </c>
-      <c r="G36" s="34">
-        <v>212874888</v>
-      </c>
-      <c r="H36" s="33">
-        <v>276571720</v>
-      </c>
-      <c r="I36" s="34">
-        <v>276571720</v>
-      </c>
-      <c r="J36" s="33">
-        <v>211090655</v>
-      </c>
-      <c r="K36" s="34">
-        <v>211090655</v>
-      </c>
-      <c r="L36" s="33">
-        <v>352172484</v>
-      </c>
-      <c r="M36" s="34">
-        <v>352172484</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" s="49" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="24">
-        <v>0</v>
-      </c>
-      <c r="C37" s="25">
-        <v>0</v>
-      </c>
-      <c r="D37" s="24"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="24">
-        <v>212874888</v>
-      </c>
-      <c r="G37" s="25">
-        <v>212874888</v>
-      </c>
-      <c r="H37" s="24">
-        <v>276571720</v>
-      </c>
-      <c r="I37" s="25">
-        <v>276571720</v>
-      </c>
-      <c r="J37" s="24">
-        <v>211090655</v>
-      </c>
-      <c r="K37" s="25">
-        <v>211090655</v>
-      </c>
-      <c r="L37" s="24">
-        <v>352172484</v>
-      </c>
-      <c r="M37" s="25">
-        <v>352172484</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="21">
-        <v>3791484583</v>
-      </c>
-      <c r="C38" s="22">
-        <v>3791484583</v>
-      </c>
-      <c r="D38" s="21">
-        <v>3971148317</v>
-      </c>
-      <c r="E38" s="22">
-        <v>3971148317</v>
-      </c>
-      <c r="F38" s="21">
-        <v>738874583</v>
-      </c>
-      <c r="G38" s="22">
-        <v>738874583</v>
-      </c>
-      <c r="H38" s="21">
-        <v>1359019257</v>
-      </c>
-      <c r="I38" s="22">
-        <v>1359019257</v>
-      </c>
-      <c r="J38" s="21">
-        <v>3191223834</v>
-      </c>
-      <c r="K38" s="22">
-        <v>3186005748</v>
-      </c>
-      <c r="L38" s="21">
-        <v>2984274710</v>
-      </c>
-      <c r="M38" s="22">
-        <v>2984274710</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" s="49" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="38"/>
-      <c r="C39" s="39"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="39"/>
-      <c r="H39" s="38"/>
-      <c r="I39" s="39"/>
-      <c r="J39" s="38"/>
-      <c r="K39" s="39"/>
-      <c r="L39" s="38"/>
-      <c r="M39" s="39"/>
-    </row>
-    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="41">
-        <f t="shared" ref="B40:M40" si="7">+B41</f>
-        <v>4234223610</v>
-      </c>
-      <c r="C40" s="42">
-        <f t="shared" si="7"/>
-        <v>2612011858</v>
-      </c>
-      <c r="D40" s="41">
-        <f t="shared" si="7"/>
-        <v>2743969420</v>
-      </c>
-      <c r="E40" s="42">
-        <f t="shared" si="7"/>
-        <v>1930804886</v>
-      </c>
-      <c r="F40" s="41">
-        <f t="shared" si="7"/>
-        <v>5192996662</v>
-      </c>
-      <c r="G40" s="42">
-        <f t="shared" si="7"/>
-        <v>5058365370</v>
-      </c>
-      <c r="H40" s="41">
-        <f t="shared" si="7"/>
-        <v>2160617226</v>
-      </c>
-      <c r="I40" s="42">
-        <f t="shared" si="7"/>
-        <v>2004154713</v>
-      </c>
-      <c r="J40" s="41">
-        <f t="shared" si="7"/>
-        <v>951878450</v>
-      </c>
-      <c r="K40" s="42">
-        <f t="shared" si="7"/>
-        <v>790069996</v>
-      </c>
-      <c r="L40" s="41">
-        <f t="shared" si="7"/>
-        <v>1026505431</v>
-      </c>
-      <c r="M40" s="42">
-        <f t="shared" si="7"/>
-        <v>651421758</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="44">
-        <f t="shared" ref="B41:M41" si="8">+B42+B63</f>
-        <v>4234223610</v>
-      </c>
-      <c r="C41" s="45">
-        <f t="shared" si="8"/>
-        <v>2612011858</v>
-      </c>
-      <c r="D41" s="44">
-        <f t="shared" si="8"/>
-        <v>2743969420</v>
-      </c>
-      <c r="E41" s="45">
-        <f t="shared" si="8"/>
-        <v>1930804886</v>
-      </c>
-      <c r="F41" s="44">
-        <f t="shared" si="8"/>
-        <v>5192996662</v>
-      </c>
-      <c r="G41" s="45">
-        <f t="shared" si="8"/>
-        <v>5058365370</v>
-      </c>
-      <c r="H41" s="44">
-        <f t="shared" si="8"/>
-        <v>2160617226</v>
-      </c>
-      <c r="I41" s="45">
-        <f t="shared" si="8"/>
-        <v>2004154713</v>
-      </c>
-      <c r="J41" s="44">
-        <f t="shared" si="8"/>
-        <v>951878450</v>
-      </c>
-      <c r="K41" s="45">
-        <f t="shared" si="8"/>
-        <v>790069996</v>
-      </c>
-      <c r="L41" s="44">
-        <f t="shared" si="8"/>
-        <v>1026505431</v>
-      </c>
-      <c r="M41" s="45">
-        <f t="shared" si="8"/>
-        <v>651421758</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B42" s="18">
-        <f>+B43+B45+B47+B52+B54+B56+B62</f>
-        <v>4108288243</v>
-      </c>
-      <c r="C42" s="19">
-        <f>+C43+C45+C47+C52+C54+C56+C62</f>
-        <v>2460063559</v>
-      </c>
-      <c r="D42" s="18">
-        <f>+D43+D45+D47+D52+D54+D56+D62</f>
-        <v>2098658881</v>
-      </c>
-      <c r="E42" s="18">
-        <f>+E43+E45+E47+E52+E54+E56+E62</f>
-        <v>1274976491</v>
-      </c>
-      <c r="F42" s="18">
-        <f t="shared" ref="F42:M42" si="9">+F43+F45+F47+F52+F54+F56+F62</f>
-        <v>4489926230</v>
-      </c>
-      <c r="G42" s="18">
-        <f t="shared" si="9"/>
-        <v>4331432481</v>
-      </c>
-      <c r="H42" s="18">
-        <f t="shared" si="9"/>
-        <v>386501938</v>
-      </c>
-      <c r="I42" s="18">
-        <f t="shared" si="9"/>
-        <v>230501938</v>
-      </c>
-      <c r="J42" s="18">
-        <f t="shared" si="9"/>
-        <v>694349853</v>
-      </c>
-      <c r="K42" s="18">
-        <f t="shared" si="9"/>
-        <v>523587352</v>
-      </c>
-      <c r="L42" s="18">
-        <f t="shared" si="9"/>
-        <v>400012274</v>
-      </c>
-      <c r="M42" s="18">
+      <c r="H26" s="16">
         <f t="shared" si="9"/>
         <v>20000000</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="20" t="s">
+      <c r="I26" s="17">
+        <f t="shared" si="9"/>
+        <v>651972457</v>
+      </c>
+      <c r="J26" s="16">
+        <f t="shared" si="9"/>
+        <v>6500000</v>
+      </c>
+      <c r="K26" s="17">
+        <f t="shared" si="9"/>
+        <v>891166756</v>
+      </c>
+      <c r="L26" s="16">
+        <f t="shared" si="9"/>
+        <v>20000000</v>
+      </c>
+      <c r="M26" s="17">
+        <f t="shared" si="9"/>
+        <v>475760377</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="44" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="19">
+        <v>72436948</v>
+      </c>
+      <c r="C27" s="20">
+        <v>124383018</v>
+      </c>
+      <c r="D27" s="19">
+        <v>47202897</v>
+      </c>
+      <c r="E27" s="20">
+        <v>245511417</v>
+      </c>
+      <c r="F27" s="19">
+        <v>30000000</v>
+      </c>
+      <c r="G27" s="20">
+        <v>470784532</v>
+      </c>
+      <c r="H27" s="19">
+        <v>20000000</v>
+      </c>
+      <c r="I27" s="20">
+        <v>651972457</v>
+      </c>
+      <c r="J27" s="19">
+        <v>6500000</v>
+      </c>
+      <c r="K27" s="20">
+        <v>891166756</v>
+      </c>
+      <c r="L27" s="19">
+        <v>20000000</v>
+      </c>
+      <c r="M27" s="20">
+        <v>475760377</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="16">
+        <f t="shared" ref="B28:M28" si="10">SUM(B29:B30)</f>
+        <v>130039513</v>
+      </c>
+      <c r="C28" s="17">
+        <f t="shared" si="10"/>
+        <v>126110941</v>
+      </c>
+      <c r="D28" s="16">
+        <f t="shared" si="10"/>
+        <v>6231706133</v>
+      </c>
+      <c r="E28" s="17">
+        <f t="shared" si="10"/>
+        <v>6231706133</v>
+      </c>
+      <c r="F28" s="16">
+        <f t="shared" si="10"/>
+        <v>674756823</v>
+      </c>
+      <c r="G28" s="17">
+        <f t="shared" si="10"/>
+        <v>674756823</v>
+      </c>
+      <c r="H28" s="16">
+        <f t="shared" si="10"/>
+        <v>3597286944</v>
+      </c>
+      <c r="I28" s="17">
+        <f t="shared" si="10"/>
+        <v>3597286944</v>
+      </c>
+      <c r="J28" s="16">
+        <f t="shared" si="10"/>
+        <v>21290824033</v>
+      </c>
+      <c r="K28" s="17">
+        <f t="shared" si="10"/>
+        <v>21277858774</v>
+      </c>
+      <c r="L28" s="16">
+        <f t="shared" si="10"/>
+        <v>13163994762</v>
+      </c>
+      <c r="M28" s="17">
+        <f t="shared" si="10"/>
+        <v>13163994762</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="44" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="19">
+        <v>126110941</v>
+      </c>
+      <c r="C29" s="20">
+        <v>126110941</v>
+      </c>
+      <c r="D29" s="19">
+        <v>5845009568</v>
+      </c>
+      <c r="E29" s="20">
+        <v>5845009568</v>
+      </c>
+      <c r="F29" s="19">
+        <v>666556823</v>
+      </c>
+      <c r="G29" s="20">
+        <v>666556823</v>
+      </c>
+      <c r="H29" s="19">
+        <v>510155245</v>
+      </c>
+      <c r="I29" s="20">
+        <v>510155245</v>
+      </c>
+      <c r="J29" s="19">
+        <v>21290824033</v>
+      </c>
+      <c r="K29" s="20">
+        <v>21277858774</v>
+      </c>
+      <c r="L29" s="19">
+        <v>12797994762</v>
+      </c>
+      <c r="M29" s="20">
+        <v>12797994762</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="19">
+        <v>3928572</v>
+      </c>
+      <c r="C30" s="20">
+        <v>0</v>
+      </c>
+      <c r="D30" s="19">
+        <v>386696565</v>
+      </c>
+      <c r="E30" s="20">
+        <v>386696565</v>
+      </c>
+      <c r="F30" s="19">
+        <v>8200000</v>
+      </c>
+      <c r="G30" s="20">
+        <v>8200000</v>
+      </c>
+      <c r="H30" s="19">
+        <v>3087131699</v>
+      </c>
+      <c r="I30" s="20">
+        <v>3087131699</v>
+      </c>
+      <c r="J30" s="19">
+        <v>0</v>
+      </c>
+      <c r="K30" s="20">
+        <v>0</v>
+      </c>
+      <c r="L30" s="19">
+        <v>366000000</v>
+      </c>
+      <c r="M30" s="20">
+        <v>366000000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="21">
+        <v>22223309</v>
+      </c>
+      <c r="C31" s="22">
+        <v>22223309</v>
+      </c>
+      <c r="D31" s="21">
+        <v>875416531</v>
+      </c>
+      <c r="E31" s="22">
+        <v>0</v>
+      </c>
+      <c r="F31" s="21">
+        <v>6792085860</v>
+      </c>
+      <c r="G31" s="22">
+        <v>6792085860</v>
+      </c>
+      <c r="H31" s="21">
+        <v>630669685</v>
+      </c>
+      <c r="I31" s="22">
+        <v>630669685</v>
+      </c>
+      <c r="J31" s="21">
+        <v>630669685</v>
+      </c>
+      <c r="K31" s="22">
+        <v>630669685</v>
+      </c>
+      <c r="L31" s="21"/>
+      <c r="M31" s="22"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="25">
+        <f t="shared" ref="B32:M33" si="11">SUM(B33:B33)</f>
+        <v>5800000000</v>
+      </c>
+      <c r="C32" s="26">
+        <f t="shared" si="11"/>
+        <v>4000000000</v>
+      </c>
+      <c r="D32" s="25">
+        <f t="shared" si="11"/>
+        <v>5000000000</v>
+      </c>
+      <c r="E32" s="26">
+        <f t="shared" si="11"/>
+        <v>5000000000</v>
+      </c>
+      <c r="F32" s="25">
+        <f t="shared" si="11"/>
+        <v>12328777860</v>
+      </c>
+      <c r="G32" s="26">
+        <f t="shared" si="11"/>
+        <v>12328777860</v>
+      </c>
+      <c r="H32" s="25">
+        <f t="shared" si="11"/>
+        <v>3004655819</v>
+      </c>
+      <c r="I32" s="26">
+        <f t="shared" si="11"/>
+        <v>3004655819</v>
+      </c>
+      <c r="J32" s="25">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="25">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M32" s="26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="28">
+        <f t="shared" si="11"/>
+        <v>5800000000</v>
+      </c>
+      <c r="C33" s="29">
+        <f t="shared" si="11"/>
+        <v>4000000000</v>
+      </c>
+      <c r="D33" s="28">
+        <f t="shared" si="11"/>
+        <v>5000000000</v>
+      </c>
+      <c r="E33" s="29">
+        <f t="shared" si="11"/>
+        <v>5000000000</v>
+      </c>
+      <c r="F33" s="28">
+        <f t="shared" si="11"/>
+        <v>12328777860</v>
+      </c>
+      <c r="G33" s="29">
+        <f t="shared" si="11"/>
+        <v>12328777860</v>
+      </c>
+      <c r="H33" s="28">
+        <f t="shared" si="11"/>
+        <v>3004655819</v>
+      </c>
+      <c r="I33" s="29">
+        <f t="shared" si="11"/>
+        <v>3004655819</v>
+      </c>
+      <c r="J33" s="28">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="29">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="28">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M33" s="29">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="19">
+        <v>5800000000</v>
+      </c>
+      <c r="C34" s="20">
+        <v>4000000000</v>
+      </c>
+      <c r="D34" s="19">
+        <v>5000000000</v>
+      </c>
+      <c r="E34" s="20">
+        <v>5000000000</v>
+      </c>
+      <c r="F34" s="19">
+        <v>12328777860</v>
+      </c>
+      <c r="G34" s="20">
+        <v>12328777860</v>
+      </c>
+      <c r="H34" s="19">
+        <v>3004655819</v>
+      </c>
+      <c r="I34" s="20">
+        <v>3004655819</v>
+      </c>
+      <c r="J34" s="19">
+        <v>0</v>
+      </c>
+      <c r="K34" s="20">
+        <v>0</v>
+      </c>
+      <c r="L34" s="19">
+        <v>0</v>
+      </c>
+      <c r="M34" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="25">
+        <f t="shared" ref="B35:M35" si="12">+B36+B38</f>
+        <v>3791484583</v>
+      </c>
+      <c r="C35" s="26">
+        <f t="shared" si="12"/>
+        <v>3791484583</v>
+      </c>
+      <c r="D35" s="25">
+        <f t="shared" si="12"/>
+        <v>3971148317</v>
+      </c>
+      <c r="E35" s="26">
+        <f t="shared" si="12"/>
+        <v>3971148317</v>
+      </c>
+      <c r="F35" s="25">
+        <f t="shared" si="12"/>
+        <v>951749471</v>
+      </c>
+      <c r="G35" s="26">
+        <f t="shared" si="12"/>
+        <v>951749471</v>
+      </c>
+      <c r="H35" s="25">
+        <f t="shared" si="12"/>
+        <v>1635590977</v>
+      </c>
+      <c r="I35" s="26">
+        <f t="shared" si="12"/>
+        <v>1635590977</v>
+      </c>
+      <c r="J35" s="25">
+        <f t="shared" si="12"/>
+        <v>3402314489</v>
+      </c>
+      <c r="K35" s="26">
+        <f t="shared" si="12"/>
+        <v>3397096403</v>
+      </c>
+      <c r="L35" s="25">
+        <f t="shared" si="12"/>
+        <v>3336447194</v>
+      </c>
+      <c r="M35" s="26">
+        <f t="shared" si="12"/>
+        <v>3336447194</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="28">
+        <f>SUM(B37:B37)</f>
+        <v>0</v>
+      </c>
+      <c r="C36" s="29">
+        <f>SUM(C37:C37)</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="28"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="28">
+        <f t="shared" ref="F36:M36" si="13">SUM(F37:F37)</f>
+        <v>212874888</v>
+      </c>
+      <c r="G36" s="29">
+        <f t="shared" si="13"/>
+        <v>212874888</v>
+      </c>
+      <c r="H36" s="28">
+        <f t="shared" si="13"/>
+        <v>276571720</v>
+      </c>
+      <c r="I36" s="29">
+        <f t="shared" si="13"/>
+        <v>276571720</v>
+      </c>
+      <c r="J36" s="28">
+        <f t="shared" si="13"/>
+        <v>211090655</v>
+      </c>
+      <c r="K36" s="29">
+        <f t="shared" si="13"/>
+        <v>211090655</v>
+      </c>
+      <c r="L36" s="28">
+        <f t="shared" si="13"/>
+        <v>352172484</v>
+      </c>
+      <c r="M36" s="29">
+        <f t="shared" si="13"/>
+        <v>352172484</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" s="44" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="19">
+        <v>0</v>
+      </c>
+      <c r="C37" s="20">
+        <v>0</v>
+      </c>
+      <c r="D37" s="19"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="19">
+        <v>212874888</v>
+      </c>
+      <c r="G37" s="20">
+        <v>212874888</v>
+      </c>
+      <c r="H37" s="19">
+        <v>276571720</v>
+      </c>
+      <c r="I37" s="20">
+        <v>276571720</v>
+      </c>
+      <c r="J37" s="19">
+        <v>211090655</v>
+      </c>
+      <c r="K37" s="20">
+        <v>211090655</v>
+      </c>
+      <c r="L37" s="19">
+        <v>352172484</v>
+      </c>
+      <c r="M37" s="20">
+        <v>352172484</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="16">
+        <v>3791484583</v>
+      </c>
+      <c r="C38" s="17">
+        <v>3791484583</v>
+      </c>
+      <c r="D38" s="16">
+        <v>3971148317</v>
+      </c>
+      <c r="E38" s="17">
+        <v>3971148317</v>
+      </c>
+      <c r="F38" s="16">
+        <v>738874583</v>
+      </c>
+      <c r="G38" s="17">
+        <v>738874583</v>
+      </c>
+      <c r="H38" s="16">
+        <v>1359019257</v>
+      </c>
+      <c r="I38" s="17">
+        <v>1359019257</v>
+      </c>
+      <c r="J38" s="16">
+        <v>3191223834</v>
+      </c>
+      <c r="K38" s="17">
+        <v>3186005748</v>
+      </c>
+      <c r="L38" s="16">
+        <v>2984274710</v>
+      </c>
+      <c r="M38" s="17">
+        <v>2984274710</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" s="44" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="33"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="34"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="34"/>
+      <c r="L39" s="33"/>
+      <c r="M39" s="34"/>
+    </row>
+    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="36">
+        <f t="shared" ref="B40:M40" si="14">+B41</f>
+        <v>4234223610</v>
+      </c>
+      <c r="C40" s="37">
+        <f t="shared" si="14"/>
+        <v>2612011858</v>
+      </c>
+      <c r="D40" s="37">
+        <f t="shared" si="14"/>
+        <v>3072074084</v>
+      </c>
+      <c r="E40" s="37">
+        <f t="shared" si="14"/>
+        <v>1976477813</v>
+      </c>
+      <c r="F40" s="36">
+        <f t="shared" si="14"/>
+        <v>5192996662</v>
+      </c>
+      <c r="G40" s="37">
+        <f t="shared" si="14"/>
+        <v>5058365370</v>
+      </c>
+      <c r="H40" s="36">
+        <f t="shared" si="14"/>
+        <v>2160617226</v>
+      </c>
+      <c r="I40" s="37">
+        <f t="shared" si="14"/>
+        <v>2004154713</v>
+      </c>
+      <c r="J40" s="36">
+        <f t="shared" si="14"/>
+        <v>951878450</v>
+      </c>
+      <c r="K40" s="37">
+        <f t="shared" si="14"/>
+        <v>790069996</v>
+      </c>
+      <c r="L40" s="36">
+        <f t="shared" si="14"/>
+        <v>1026505431</v>
+      </c>
+      <c r="M40" s="37">
+        <f t="shared" si="14"/>
+        <v>651421758</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="39">
+        <f t="shared" ref="B41:M41" si="15">+B42+B63</f>
+        <v>4234223610</v>
+      </c>
+      <c r="C41" s="40">
+        <f t="shared" si="15"/>
+        <v>2612011858</v>
+      </c>
+      <c r="D41" s="40">
+        <f t="shared" si="15"/>
+        <v>3072074084</v>
+      </c>
+      <c r="E41" s="40">
+        <f t="shared" si="15"/>
+        <v>1976477813</v>
+      </c>
+      <c r="F41" s="39">
+        <f t="shared" si="15"/>
+        <v>5192996662</v>
+      </c>
+      <c r="G41" s="40">
+        <f t="shared" si="15"/>
+        <v>5058365370</v>
+      </c>
+      <c r="H41" s="39">
+        <f t="shared" si="15"/>
+        <v>2160617226</v>
+      </c>
+      <c r="I41" s="40">
+        <f t="shared" si="15"/>
+        <v>2004154713</v>
+      </c>
+      <c r="J41" s="39">
+        <f t="shared" si="15"/>
+        <v>951878450</v>
+      </c>
+      <c r="K41" s="40">
+        <f t="shared" si="15"/>
+        <v>790069996</v>
+      </c>
+      <c r="L41" s="39">
+        <f t="shared" si="15"/>
+        <v>1026505431</v>
+      </c>
+      <c r="M41" s="40">
+        <f t="shared" si="15"/>
+        <v>651421758</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="13">
+        <f t="shared" ref="B42:M42" si="16">+B43+B45+B47+B52+B54+B56+B62</f>
+        <v>4108288243</v>
+      </c>
+      <c r="C42" s="14">
+        <f t="shared" si="16"/>
+        <v>2460063559</v>
+      </c>
+      <c r="D42" s="14">
+        <f t="shared" si="16"/>
+        <v>2426763545</v>
+      </c>
+      <c r="E42" s="14">
+        <f t="shared" si="16"/>
+        <v>1320649418</v>
+      </c>
+      <c r="F42" s="13">
+        <f t="shared" si="16"/>
+        <v>4489926230</v>
+      </c>
+      <c r="G42" s="13">
+        <f t="shared" si="16"/>
+        <v>4331432481</v>
+      </c>
+      <c r="H42" s="13">
+        <f t="shared" si="16"/>
+        <v>386501938</v>
+      </c>
+      <c r="I42" s="13">
+        <f t="shared" si="16"/>
+        <v>230501938</v>
+      </c>
+      <c r="J42" s="13">
+        <f t="shared" si="16"/>
+        <v>694349853</v>
+      </c>
+      <c r="K42" s="13">
+        <f t="shared" si="16"/>
+        <v>523587352</v>
+      </c>
+      <c r="L42" s="13">
+        <f t="shared" si="16"/>
+        <v>400012274</v>
+      </c>
+      <c r="M42" s="13">
+        <f t="shared" si="16"/>
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B43" s="21">
+      <c r="B43" s="16">
+        <f>SUM(B44:B44)</f>
         <v>37033544</v>
       </c>
-      <c r="C43" s="22">
+      <c r="C43" s="17">
+        <f>SUM(C44:C44)</f>
         <v>37033544</v>
       </c>
-      <c r="D43" s="21">
+      <c r="D43" s="16">
+        <f>SUM(D44:D44)</f>
         <v>29626715</v>
       </c>
-      <c r="E43" s="22">
+      <c r="E43" s="17">
+        <f>SUM(E44:E44)</f>
         <v>29626715</v>
       </c>
-      <c r="F43" s="21"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="22"/>
-      <c r="J43" s="21"/>
-      <c r="K43" s="22"/>
-      <c r="L43" s="21">
+      <c r="F43" s="16"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="16"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="16"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="16">
+        <f>SUM(L44:L44)</f>
         <v>3648640</v>
       </c>
-      <c r="M43" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" s="49" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="23" t="s">
+      <c r="M43" s="17">
+        <f>SUM(M44:M44)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" s="44" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="24">
+      <c r="B44" s="19">
         <v>37033544</v>
       </c>
-      <c r="C44" s="25">
+      <c r="C44" s="20">
         <v>37033544</v>
       </c>
-      <c r="D44" s="24">
+      <c r="D44" s="19">
         <v>29626715</v>
       </c>
-      <c r="E44" s="25">
+      <c r="E44" s="20">
         <v>29626715</v>
       </c>
-      <c r="F44" s="24"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="24"/>
-      <c r="I44" s="25"/>
-      <c r="J44" s="24"/>
-      <c r="K44" s="25"/>
-      <c r="L44" s="24">
+      <c r="F44" s="19"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="19">
         <v>3648640</v>
       </c>
-      <c r="M44" s="25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="20" t="s">
+      <c r="M44" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="21">
+      <c r="B45" s="16">
+        <f t="shared" ref="B45:K45" si="17">SUM(B46:B46)</f>
         <v>38936971</v>
       </c>
-      <c r="C45" s="22">
+      <c r="C45" s="17">
+        <f t="shared" si="17"/>
         <v>38936971</v>
       </c>
-      <c r="D45" s="21">
+      <c r="D45" s="16">
+        <f t="shared" si="17"/>
         <v>39256400</v>
       </c>
-      <c r="E45" s="22">
+      <c r="E45" s="17">
+        <f t="shared" si="17"/>
         <v>39256400</v>
       </c>
-      <c r="F45" s="21">
+      <c r="F45" s="16">
+        <f t="shared" si="17"/>
         <v>31249680</v>
       </c>
-      <c r="G45" s="22">
+      <c r="G45" s="17">
+        <f t="shared" si="17"/>
         <v>31249680</v>
       </c>
-      <c r="H45" s="21">
+      <c r="H45" s="16">
+        <f t="shared" si="17"/>
         <v>33257139</v>
       </c>
-      <c r="I45" s="22">
+      <c r="I45" s="17">
+        <f t="shared" si="17"/>
         <v>33257139</v>
       </c>
-      <c r="J45" s="21">
+      <c r="J45" s="16">
+        <f t="shared" si="17"/>
         <v>35112120</v>
       </c>
-      <c r="K45" s="22">
+      <c r="K45" s="17">
+        <f t="shared" si="17"/>
         <v>35112120</v>
       </c>
-      <c r="L45" s="21"/>
-      <c r="M45" s="22"/>
-    </row>
-    <row r="46" spans="1:13" s="49" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="23" t="s">
+      <c r="L45" s="16"/>
+      <c r="M45" s="17"/>
+    </row>
+    <row r="46" spans="1:13" s="44" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="24">
+      <c r="B46" s="19">
         <v>38936971</v>
       </c>
-      <c r="C46" s="25">
+      <c r="C46" s="20">
         <v>38936971</v>
       </c>
-      <c r="D46" s="24">
+      <c r="D46" s="19">
         <v>39256400</v>
       </c>
-      <c r="E46" s="25">
+      <c r="E46" s="20">
         <v>39256400</v>
       </c>
-      <c r="F46" s="24">
+      <c r="F46" s="19">
         <v>31249680</v>
       </c>
-      <c r="G46" s="25">
+      <c r="G46" s="20">
         <v>31249680</v>
       </c>
-      <c r="H46" s="24">
+      <c r="H46" s="19">
         <v>33257139</v>
       </c>
-      <c r="I46" s="25">
+      <c r="I46" s="20">
         <v>33257139</v>
       </c>
-      <c r="J46" s="24">
+      <c r="J46" s="19">
         <v>35112120</v>
       </c>
-      <c r="K46" s="25">
+      <c r="K46" s="20">
         <v>35112120</v>
       </c>
-      <c r="L46" s="24"/>
-      <c r="M46" s="25"/>
-    </row>
-    <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="20" t="s">
+      <c r="L46" s="19"/>
+      <c r="M46" s="20"/>
+    </row>
+    <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="21">
+      <c r="B47" s="16">
+        <f t="shared" ref="B47:L47" si="18">SUM(B48:B51)</f>
         <v>4032317728</v>
       </c>
-      <c r="C47" s="22">
+      <c r="C47" s="17">
+        <f t="shared" si="18"/>
         <v>2384093044</v>
       </c>
-      <c r="D47" s="21">
+      <c r="D47" s="16">
+        <f t="shared" si="18"/>
         <v>2029775766</v>
       </c>
-      <c r="E47" s="22">
+      <c r="E47" s="17">
+        <f t="shared" si="18"/>
         <v>1206093376</v>
       </c>
-      <c r="F47" s="21">
+      <c r="F47" s="16">
+        <f t="shared" si="18"/>
         <v>1423506806</v>
       </c>
-      <c r="G47" s="22">
+      <c r="G47" s="17">
+        <f t="shared" si="18"/>
         <v>1423506807</v>
       </c>
-      <c r="H47" s="21">
+      <c r="H47" s="16">
+        <f t="shared" si="18"/>
         <v>50000000</v>
       </c>
-      <c r="I47" s="22">
+      <c r="I47" s="17">
+        <f t="shared" si="18"/>
         <v>44000000</v>
       </c>
-      <c r="J47" s="21">
+      <c r="J47" s="16">
+        <f t="shared" si="18"/>
         <v>230000000</v>
       </c>
-      <c r="K47" s="22">
-        <v>0</v>
-      </c>
-      <c r="L47" s="21">
+      <c r="K47" s="17">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="L47" s="16">
+        <f t="shared" si="18"/>
         <v>115000000</v>
       </c>
-      <c r="M47" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" s="49" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="23" t="s">
+      <c r="M47" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" s="44" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="24">
+      <c r="B48" s="19">
         <v>3952317728</v>
       </c>
-      <c r="C48" s="25">
+      <c r="C48" s="20">
         <v>2384093044</v>
       </c>
-      <c r="D48" s="24">
+      <c r="D48" s="19">
         <v>2029775766</v>
       </c>
-      <c r="E48" s="25">
+      <c r="E48" s="20">
         <v>1206093376</v>
       </c>
-      <c r="F48" s="24">
+      <c r="F48" s="19">
         <v>521116307</v>
       </c>
-      <c r="G48" s="25">
+      <c r="G48" s="20">
         <v>521116307</v>
       </c>
-      <c r="H48" s="24">
+      <c r="H48" s="19">
         <v>20000000</v>
       </c>
-      <c r="I48" s="25">
+      <c r="I48" s="20">
         <v>14000000</v>
       </c>
-      <c r="J48" s="24">
+      <c r="J48" s="19">
         <v>100000000</v>
       </c>
-      <c r="K48" s="25">
-        <v>0</v>
-      </c>
-      <c r="L48" s="24">
+      <c r="K48" s="20">
+        <v>0</v>
+      </c>
+      <c r="L48" s="19">
         <v>50000000</v>
       </c>
-      <c r="M48" s="25"/>
-    </row>
-    <row r="49" spans="1:13" s="49" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="23" t="s">
+      <c r="M48" s="20"/>
+    </row>
+    <row r="49" spans="1:13" s="44" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="B49" s="24">
+      <c r="B49" s="19">
         <v>50000000</v>
       </c>
-      <c r="C49" s="25">
-        <v>0</v>
-      </c>
-      <c r="D49" s="24"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="25"/>
-      <c r="H49" s="24"/>
-      <c r="I49" s="25"/>
-      <c r="J49" s="24"/>
-      <c r="K49" s="25"/>
-      <c r="L49" s="24"/>
-      <c r="M49" s="25"/>
-    </row>
-    <row r="50" spans="1:13" s="49" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="23" t="s">
+      <c r="C49" s="20">
+        <v>0</v>
+      </c>
+      <c r="D49" s="19"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="19"/>
+      <c r="K49" s="20"/>
+      <c r="L49" s="19"/>
+      <c r="M49" s="20"/>
+    </row>
+    <row r="50" spans="1:13" s="44" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="B50" s="24">
+      <c r="B50" s="19">
         <v>30000000</v>
       </c>
-      <c r="C50" s="25">
-        <v>0</v>
-      </c>
-      <c r="D50" s="24"/>
-      <c r="E50" s="25"/>
-      <c r="F50" s="24">
+      <c r="C50" s="20">
+        <v>0</v>
+      </c>
+      <c r="D50" s="19"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="19">
         <v>107850000</v>
       </c>
-      <c r="G50" s="25">
+      <c r="G50" s="20">
         <v>107850000</v>
       </c>
-      <c r="H50" s="24">
+      <c r="H50" s="19">
         <v>30000000</v>
       </c>
-      <c r="I50" s="25">
+      <c r="I50" s="20">
         <v>30000000</v>
       </c>
-      <c r="J50" s="24">
+      <c r="J50" s="19">
         <v>60000000</v>
       </c>
-      <c r="K50" s="25">
-        <v>0</v>
-      </c>
-      <c r="L50" s="24">
+      <c r="K50" s="20">
+        <v>0</v>
+      </c>
+      <c r="L50" s="19">
         <v>30000000</v>
       </c>
-      <c r="M50" s="25"/>
-    </row>
-    <row r="51" spans="1:13" s="49" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="23" t="s">
+      <c r="M50" s="20"/>
+    </row>
+    <row r="51" spans="1:13" s="44" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="B51" s="24"/>
-      <c r="C51" s="25"/>
-      <c r="D51" s="24"/>
-      <c r="E51" s="25"/>
-      <c r="F51" s="24">
+      <c r="B51" s="19"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="19">
         <v>794540499</v>
       </c>
-      <c r="G51" s="25">
+      <c r="G51" s="20">
         <v>794540500</v>
       </c>
-      <c r="H51" s="24"/>
-      <c r="I51" s="25"/>
-      <c r="J51" s="24">
+      <c r="H51" s="19"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="19">
         <v>70000000</v>
       </c>
-      <c r="K51" s="25">
-        <v>0</v>
-      </c>
-      <c r="L51" s="24">
+      <c r="K51" s="20">
+        <v>0</v>
+      </c>
+      <c r="L51" s="19">
         <v>35000000</v>
       </c>
-      <c r="M51" s="25"/>
-    </row>
-    <row r="52" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="20" t="s">
+      <c r="M51" s="20"/>
+    </row>
+    <row r="52" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="B52" s="21"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="21">
+      <c r="B52" s="16"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="16">
+        <f>SUM(F53:F53)</f>
         <v>50000000</v>
       </c>
-      <c r="G52" s="22">
-        <v>0</v>
-      </c>
-      <c r="H52" s="21">
+      <c r="G52" s="17">
+        <v>0</v>
+      </c>
+      <c r="H52" s="16">
+        <f>SUM(H53:H53)</f>
         <v>150000000</v>
       </c>
-      <c r="I52" s="22">
-        <v>0</v>
-      </c>
-      <c r="J52" s="21">
+      <c r="I52" s="17">
+        <v>0</v>
+      </c>
+      <c r="J52" s="16">
+        <f>SUM(J53:J53)</f>
         <v>350000000</v>
       </c>
-      <c r="K52" s="22">
+      <c r="K52" s="17">
         <v>379999766</v>
       </c>
-      <c r="L52" s="21">
+      <c r="L52" s="16">
+        <f>SUM(L53:L53)</f>
         <v>281363634</v>
       </c>
-      <c r="M52" s="22">
+      <c r="M52" s="17">
         <v>20000000</v>
       </c>
     </row>
-    <row r="53" spans="1:13" s="49" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="35" t="s">
+    <row r="53" spans="1:13" s="44" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="B53" s="24"/>
-      <c r="C53" s="25"/>
-      <c r="D53" s="24"/>
-      <c r="E53" s="25"/>
-      <c r="F53" s="24">
+      <c r="B53" s="19"/>
+      <c r="C53" s="20"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="19">
         <v>50000000</v>
       </c>
-      <c r="G53" s="25"/>
-      <c r="H53" s="24">
+      <c r="G53" s="20"/>
+      <c r="H53" s="19">
         <v>150000000</v>
       </c>
-      <c r="I53" s="25"/>
-      <c r="J53" s="24">
+      <c r="I53" s="20"/>
+      <c r="J53" s="19">
         <v>350000000</v>
       </c>
-      <c r="K53" s="25"/>
-      <c r="L53" s="24">
+      <c r="K53" s="20"/>
+      <c r="L53" s="19">
         <v>281363634</v>
       </c>
-      <c r="M53" s="25"/>
-    </row>
-    <row r="54" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="46" t="s">
+      <c r="M53" s="20"/>
+    </row>
+    <row r="54" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="B54" s="21"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="21">
+      <c r="B54" s="16"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="16">
+        <f>SUM(H55:H55)</f>
         <v>30000000</v>
       </c>
-      <c r="I54" s="22">
+      <c r="I54" s="17">
+        <f>SUM(I55:I55)</f>
         <v>30000000</v>
       </c>
-      <c r="J54" s="21"/>
-      <c r="K54" s="22"/>
-      <c r="L54" s="21"/>
-      <c r="M54" s="22"/>
-    </row>
-    <row r="55" spans="1:13" s="49" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="35" t="s">
+      <c r="J54" s="16"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="16"/>
+      <c r="M54" s="17"/>
+    </row>
+    <row r="55" spans="1:13" s="44" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B55" s="24"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="24"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="24">
+      <c r="B55" s="19"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="20"/>
+      <c r="H55" s="19">
         <v>30000000</v>
       </c>
-      <c r="I55" s="25">
+      <c r="I55" s="20">
         <v>30000000</v>
       </c>
-      <c r="J55" s="24"/>
-      <c r="K55" s="25"/>
-      <c r="L55" s="24"/>
-      <c r="M55" s="25"/>
-    </row>
-    <row r="56" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="20" t="s">
+      <c r="J55" s="19"/>
+      <c r="K55" s="20"/>
+      <c r="L55" s="19"/>
+      <c r="M55" s="20"/>
+    </row>
+    <row r="56" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="B56" s="21"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="21">
+      <c r="B56" s="16"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="52">
+        <f t="shared" ref="D56:K56" si="19">SUM(D57:D61)</f>
+        <v>328104664</v>
+      </c>
+      <c r="E56" s="53">
+        <f t="shared" si="19"/>
+        <v>45672927</v>
+      </c>
+      <c r="F56" s="16">
+        <f t="shared" si="19"/>
         <v>585169744</v>
       </c>
-      <c r="G56" s="22">
+      <c r="G56" s="17">
+        <f t="shared" si="19"/>
         <v>476675994</v>
       </c>
-      <c r="H56" s="21">
+      <c r="H56" s="16">
+        <f t="shared" si="19"/>
         <v>123244799</v>
       </c>
-      <c r="I56" s="22">
+      <c r="I56" s="17">
+        <f t="shared" si="19"/>
         <v>123244799</v>
       </c>
-      <c r="J56" s="21">
+      <c r="J56" s="16">
+        <f t="shared" si="19"/>
         <v>79237733</v>
       </c>
-      <c r="K56" s="22">
+      <c r="K56" s="17">
+        <f t="shared" si="19"/>
         <v>108475466</v>
       </c>
-      <c r="L56" s="21"/>
-      <c r="M56" s="22"/>
-    </row>
-    <row r="57" spans="1:13" s="49" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="35" t="s">
+      <c r="L56" s="16"/>
+      <c r="M56" s="17"/>
+    </row>
+    <row r="57" spans="1:13" s="44" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="B57" s="24"/>
-      <c r="C57" s="25"/>
-      <c r="D57" s="24">
+      <c r="B57" s="19"/>
+      <c r="C57" s="20"/>
+      <c r="D57" s="19">
         <v>328104664</v>
       </c>
-      <c r="E57" s="25">
+      <c r="E57" s="20">
         <v>45672927</v>
       </c>
-      <c r="F57" s="24">
+      <c r="F57" s="19">
         <v>327329444</v>
       </c>
-      <c r="G57" s="25">
+      <c r="G57" s="20">
         <v>233712569</v>
       </c>
-      <c r="H57" s="24">
+      <c r="H57" s="19">
         <v>123244799</v>
       </c>
-      <c r="I57" s="25">
+      <c r="I57" s="20">
         <v>123244799</v>
       </c>
-      <c r="J57" s="24">
+      <c r="J57" s="19">
         <v>50000000</v>
       </c>
-      <c r="K57" s="25">
+      <c r="K57" s="20">
         <v>50000000</v>
       </c>
-      <c r="L57" s="24"/>
-      <c r="M57" s="25"/>
-    </row>
-    <row r="58" spans="1:13" s="49" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="35" t="s">
+      <c r="L57" s="19"/>
+      <c r="M57" s="20"/>
+    </row>
+    <row r="58" spans="1:13" s="44" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="B58" s="24"/>
-      <c r="C58" s="25"/>
-      <c r="D58" s="24"/>
-      <c r="E58" s="25"/>
-      <c r="F58" s="24">
+      <c r="B58" s="19"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="19">
         <v>49293000</v>
       </c>
-      <c r="G58" s="25">
+      <c r="G58" s="20">
         <v>24821269</v>
       </c>
-      <c r="H58" s="24"/>
-      <c r="I58" s="25"/>
-      <c r="J58" s="24"/>
-      <c r="K58" s="25"/>
-      <c r="L58" s="24"/>
-      <c r="M58" s="25"/>
-    </row>
-    <row r="59" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="35" t="s">
+      <c r="H58" s="19"/>
+      <c r="I58" s="20"/>
+      <c r="J58" s="19"/>
+      <c r="K58" s="20"/>
+      <c r="L58" s="19"/>
+      <c r="M58" s="20"/>
+    </row>
+    <row r="59" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="B59" s="21"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="21">
+      <c r="B59" s="16"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="16">
         <v>189588400</v>
       </c>
-      <c r="G59" s="22">
+      <c r="G59" s="17">
         <v>198311051</v>
       </c>
-      <c r="H59" s="21"/>
-      <c r="I59" s="22"/>
-      <c r="J59" s="21"/>
-      <c r="K59" s="22"/>
-      <c r="L59" s="21"/>
-      <c r="M59" s="22"/>
-    </row>
-    <row r="60" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="35" t="s">
+      <c r="H59" s="16"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="16"/>
+      <c r="K59" s="17"/>
+      <c r="L59" s="16"/>
+      <c r="M59" s="17"/>
+    </row>
+    <row r="60" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="B60" s="21"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="21">
+      <c r="B60" s="16"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="16">
         <v>18958900</v>
       </c>
-      <c r="G60" s="22">
+      <c r="G60" s="17">
         <v>19831105</v>
       </c>
-      <c r="H60" s="21"/>
-      <c r="I60" s="22"/>
-      <c r="J60" s="21"/>
-      <c r="K60" s="22"/>
-      <c r="L60" s="21"/>
-      <c r="M60" s="22"/>
-    </row>
-    <row r="61" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="35" t="s">
+      <c r="H60" s="16"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="16"/>
+      <c r="K60" s="17"/>
+      <c r="L60" s="16"/>
+      <c r="M60" s="17"/>
+    </row>
+    <row r="61" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="B61" s="21"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="21"/>
-      <c r="G61" s="22"/>
-      <c r="H61" s="21"/>
-      <c r="I61" s="22"/>
-      <c r="J61" s="21">
+      <c r="B61" s="16"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="17"/>
+      <c r="H61" s="16"/>
+      <c r="I61" s="17"/>
+      <c r="J61" s="16">
         <v>29237733</v>
       </c>
-      <c r="K61" s="22">
+      <c r="K61" s="17">
         <v>58475466</v>
       </c>
-      <c r="L61" s="21"/>
-      <c r="M61" s="22"/>
-    </row>
-    <row r="62" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="28" t="s">
+      <c r="L61" s="16"/>
+      <c r="M61" s="17"/>
+    </row>
+    <row r="62" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B62" s="21"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="21">
+      <c r="B62" s="16"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="16">
         <v>2400000000</v>
       </c>
-      <c r="G62" s="22">
+      <c r="G62" s="17">
         <v>2400000000</v>
       </c>
-      <c r="H62" s="21"/>
-      <c r="I62" s="22"/>
-      <c r="J62" s="21"/>
-      <c r="K62" s="22"/>
-      <c r="L62" s="21"/>
-      <c r="M62" s="22"/>
-    </row>
-    <row r="63" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="17" t="s">
+      <c r="H62" s="16"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="16"/>
+      <c r="K62" s="17"/>
+      <c r="L62" s="16"/>
+      <c r="M62" s="17"/>
+    </row>
+    <row r="63" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B63" s="18">
-        <f>+B64+B66</f>
+      <c r="B63" s="13">
+        <f t="shared" ref="B63:M63" si="20">+B64+B66</f>
         <v>125935367</v>
       </c>
-      <c r="C63" s="47">
-        <f>+C64+C66</f>
+      <c r="C63" s="42">
+        <f t="shared" si="20"/>
         <v>151948299</v>
       </c>
-      <c r="D63" s="18">
-        <f>+D64+D66</f>
+      <c r="D63" s="13">
+        <f t="shared" si="20"/>
         <v>645310539</v>
       </c>
-      <c r="E63" s="18">
-        <f t="shared" ref="E63:M63" si="10">+E64+E66</f>
+      <c r="E63" s="13">
+        <f t="shared" si="20"/>
         <v>655828395</v>
       </c>
-      <c r="F63" s="18">
-        <f t="shared" si="10"/>
+      <c r="F63" s="13">
+        <f t="shared" si="20"/>
         <v>703070432</v>
       </c>
-      <c r="G63" s="18">
-        <f t="shared" si="10"/>
+      <c r="G63" s="13">
+        <f t="shared" si="20"/>
         <v>726932889</v>
       </c>
-      <c r="H63" s="18">
-        <f t="shared" si="10"/>
+      <c r="H63" s="13">
+        <f t="shared" si="20"/>
         <v>1774115288</v>
       </c>
-      <c r="I63" s="18">
-        <f t="shared" si="10"/>
+      <c r="I63" s="13">
+        <f t="shared" si="20"/>
         <v>1773652775</v>
       </c>
-      <c r="J63" s="18">
-        <f t="shared" si="10"/>
+      <c r="J63" s="13">
+        <f t="shared" si="20"/>
         <v>257528597</v>
       </c>
-      <c r="K63" s="18">
-        <f t="shared" si="10"/>
+      <c r="K63" s="13">
+        <f t="shared" si="20"/>
         <v>266482644</v>
       </c>
-      <c r="L63" s="18">
-        <f t="shared" si="10"/>
+      <c r="L63" s="13">
+        <f t="shared" si="20"/>
         <v>626493157</v>
       </c>
-      <c r="M63" s="18">
-        <f t="shared" si="10"/>
+      <c r="M63" s="13">
+        <f t="shared" si="20"/>
         <v>631421758</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="20" t="s">
+    <row r="64" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B64" s="21">
-        <v>0</v>
-      </c>
-      <c r="C64" s="22">
+      <c r="B64" s="16">
+        <f t="shared" ref="B64:M64" si="21">SUM(B65:B65)</f>
+        <v>0</v>
+      </c>
+      <c r="C64" s="17">
+        <f t="shared" si="21"/>
         <v>26012932</v>
       </c>
-      <c r="D64" s="21">
+      <c r="D64" s="16">
+        <f t="shared" si="21"/>
         <v>28246648</v>
       </c>
-      <c r="E64" s="22">
+      <c r="E64" s="17">
+        <f t="shared" si="21"/>
         <v>38764504</v>
       </c>
-      <c r="F64" s="21">
+      <c r="F64" s="16">
+        <f t="shared" si="21"/>
         <v>32000000</v>
       </c>
-      <c r="G64" s="22">
+      <c r="G64" s="17">
+        <f t="shared" si="21"/>
         <v>55862457</v>
       </c>
-      <c r="H64" s="21">
+      <c r="H64" s="16">
+        <f t="shared" si="21"/>
         <v>11336593</v>
       </c>
-      <c r="I64" s="22">
+      <c r="I64" s="17">
+        <f t="shared" si="21"/>
         <v>10874080</v>
       </c>
-      <c r="J64" s="21">
+      <c r="J64" s="16">
+        <f t="shared" si="21"/>
         <v>750000</v>
       </c>
-      <c r="K64" s="22">
+      <c r="K64" s="17">
+        <f t="shared" si="21"/>
         <v>10652047</v>
       </c>
-      <c r="L64" s="21">
+      <c r="L64" s="16">
+        <f t="shared" si="21"/>
         <v>700000</v>
       </c>
-      <c r="M64" s="22">
+      <c r="M64" s="17">
+        <f t="shared" si="21"/>
         <v>5628601</v>
       </c>
     </row>
-    <row r="65" spans="1:13" s="49" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="35" t="s">
+    <row r="65" spans="1:13" s="44" customFormat="1" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="B65" s="24">
-        <v>0</v>
-      </c>
-      <c r="C65" s="25">
+      <c r="B65" s="19">
+        <v>0</v>
+      </c>
+      <c r="C65" s="20">
         <v>26012932</v>
       </c>
-      <c r="D65" s="24">
+      <c r="D65" s="19">
         <v>28246648</v>
       </c>
-      <c r="E65" s="25">
+      <c r="E65" s="20">
         <v>38764504</v>
       </c>
-      <c r="F65" s="24">
+      <c r="F65" s="19">
         <v>32000000</v>
       </c>
-      <c r="G65" s="25">
+      <c r="G65" s="20">
         <v>55862457</v>
       </c>
-      <c r="H65" s="24">
+      <c r="H65" s="19">
         <v>11336593</v>
       </c>
-      <c r="I65" s="25">
+      <c r="I65" s="20">
         <v>10874080</v>
       </c>
-      <c r="J65" s="24">
+      <c r="J65" s="19">
         <v>750000</v>
       </c>
-      <c r="K65" s="25">
+      <c r="K65" s="20">
         <v>10652047</v>
       </c>
-      <c r="L65" s="24">
+      <c r="L65" s="19">
         <v>700000</v>
       </c>
-      <c r="M65" s="25">
+      <c r="M65" s="20">
         <v>5628601</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="20" t="s">
+    <row r="66" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B66" s="21">
+      <c r="B66" s="16">
+        <f t="shared" ref="B66:M66" si="22">SUM(B67:B69)</f>
         <v>125935367</v>
       </c>
-      <c r="C66" s="22">
+      <c r="C66" s="17">
+        <f t="shared" si="22"/>
         <v>125935367</v>
       </c>
-      <c r="D66" s="21">
+      <c r="D66" s="16">
+        <f t="shared" si="22"/>
         <v>617063891</v>
       </c>
-      <c r="E66" s="22">
+      <c r="E66" s="17">
+        <f t="shared" si="22"/>
         <v>617063891</v>
       </c>
-      <c r="F66" s="21">
+      <c r="F66" s="16">
+        <f t="shared" si="22"/>
         <v>671070432</v>
       </c>
-      <c r="G66" s="22">
+      <c r="G66" s="17">
+        <f t="shared" si="22"/>
         <v>671070432</v>
       </c>
-      <c r="H66" s="21">
+      <c r="H66" s="16">
+        <f t="shared" si="22"/>
         <v>1762778695</v>
       </c>
-      <c r="I66" s="22">
+      <c r="I66" s="17">
+        <f t="shared" si="22"/>
         <v>1762778695</v>
       </c>
-      <c r="J66" s="21">
+      <c r="J66" s="16">
+        <f t="shared" si="22"/>
         <v>256778597</v>
       </c>
-      <c r="K66" s="22">
+      <c r="K66" s="17">
+        <f t="shared" si="22"/>
         <v>255830597</v>
       </c>
-      <c r="L66" s="21">
+      <c r="L66" s="16">
+        <f t="shared" si="22"/>
         <v>625793157</v>
       </c>
-      <c r="M66" s="22">
+      <c r="M66" s="17">
+        <f t="shared" si="22"/>
         <v>625793157</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="23" t="s">
+    <row r="67" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="B67" s="24">
+      <c r="B67" s="19">
         <v>75481319</v>
       </c>
-      <c r="C67" s="25">
+      <c r="C67" s="20">
         <v>75481319</v>
       </c>
-      <c r="D67" s="24">
+      <c r="D67" s="19">
         <v>47033544</v>
       </c>
-      <c r="E67" s="25">
+      <c r="E67" s="20">
         <v>47033544</v>
       </c>
-      <c r="F67" s="24">
+      <c r="F67" s="19">
         <v>70546400</v>
       </c>
-      <c r="G67" s="25">
+      <c r="G67" s="20">
         <v>70546400</v>
       </c>
-      <c r="H67" s="24">
+      <c r="H67" s="19">
         <v>334027056</v>
       </c>
-      <c r="I67" s="25">
+      <c r="I67" s="20">
         <v>334027056</v>
       </c>
-      <c r="J67" s="24">
+      <c r="J67" s="19">
         <v>104491205</v>
       </c>
-      <c r="K67" s="25">
+      <c r="K67" s="20">
         <v>104491205</v>
       </c>
-      <c r="L67" s="24">
+      <c r="L67" s="19">
         <v>141538509</v>
       </c>
-      <c r="M67" s="25">
+      <c r="M67" s="20">
         <v>141538509</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="23" t="s">
+    <row r="68" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="B68" s="24">
+      <c r="B68" s="19">
         <v>40454048</v>
       </c>
-      <c r="C68" s="25">
+      <c r="C68" s="20">
         <v>40454048</v>
       </c>
-      <c r="D68" s="24">
+      <c r="D68" s="19">
         <v>555030347</v>
       </c>
-      <c r="E68" s="25">
+      <c r="E68" s="20">
         <v>555030347</v>
       </c>
-      <c r="F68" s="24">
+      <c r="F68" s="19">
         <v>556519032</v>
       </c>
-      <c r="G68" s="25">
+      <c r="G68" s="20">
         <v>556519032</v>
       </c>
-      <c r="H68" s="24">
+      <c r="H68" s="19">
         <v>1400171699</v>
       </c>
-      <c r="I68" s="25">
+      <c r="I68" s="20">
         <v>1400171699</v>
       </c>
-      <c r="J68" s="24">
+      <c r="J68" s="19">
         <v>15062987</v>
       </c>
-      <c r="K68" s="25">
+      <c r="K68" s="20">
         <v>14114987</v>
       </c>
-      <c r="L68" s="24">
+      <c r="L68" s="19">
         <v>240297715</v>
       </c>
-      <c r="M68" s="25">
+      <c r="M68" s="20">
         <v>240297715</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="37" t="s">
+    <row r="69" spans="1:13" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="B69" s="38">
+      <c r="B69" s="33">
         <v>10000000</v>
       </c>
-      <c r="C69" s="39">
+      <c r="C69" s="34">
         <v>10000000</v>
       </c>
-      <c r="D69" s="38">
+      <c r="D69" s="33">
         <v>15000000</v>
       </c>
-      <c r="E69" s="39">
+      <c r="E69" s="34">
         <v>15000000</v>
       </c>
-      <c r="F69" s="38">
+      <c r="F69" s="33">
         <v>44005000</v>
       </c>
-      <c r="G69" s="39">
+      <c r="G69" s="34">
         <v>44005000</v>
       </c>
-      <c r="H69" s="38">
+      <c r="H69" s="33">
         <v>28579940</v>
       </c>
-      <c r="I69" s="39">
+      <c r="I69" s="34">
         <v>28579940</v>
       </c>
-      <c r="J69" s="38">
+      <c r="J69" s="33">
         <v>137224405</v>
       </c>
-      <c r="K69" s="39">
+      <c r="K69" s="34">
         <v>137224405</v>
       </c>
-      <c r="L69" s="38">
+      <c r="L69" s="33">
         <v>243956933</v>
       </c>
-      <c r="M69" s="39">
+      <c r="M69" s="34">
         <v>243956933</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="J3:K3"/>
     <mergeCell ref="A1:M2"/>
+    <mergeCell ref="B3:C3"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:C3"/>
     <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
     <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
